--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.49060026249564</v>
+        <v>9.992222542655542</v>
       </c>
       <c r="D2" t="n">
-        <v>57.84177480766956</v>
+        <v>9.399288406246304</v>
       </c>
       <c r="E2" t="n">
-        <v>10.30160588505072</v>
+        <v>1.674010956320741</v>
       </c>
       <c r="F2" t="n">
-        <v>14.88017231015632</v>
+        <v>2.418028000400402</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.5445761451414</v>
+        <v>8.700993623585477</v>
       </c>
       <c r="D3" t="n">
-        <v>50.39904388717891</v>
+        <v>8.189844631666572</v>
       </c>
       <c r="E3" t="n">
-        <v>10.30160588505072</v>
+        <v>1.674010956320741</v>
       </c>
       <c r="F3" t="n">
-        <v>14.88017231015632</v>
+        <v>2.418028000400402</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.97703816688148</v>
+        <v>9.908768702118241</v>
       </c>
       <c r="D4" t="n">
-        <v>57.08673113978016</v>
+        <v>9.276593810214276</v>
       </c>
       <c r="E4" t="n">
-        <v>10.30160588505072</v>
+        <v>1.674010956320741</v>
       </c>
       <c r="F4" t="n">
-        <v>14.88017231015632</v>
+        <v>2.418028000400402</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.93104130171903</v>
+        <v>6.326294211529343</v>
       </c>
       <c r="D5" t="n">
-        <v>37.56838231505109</v>
+        <v>6.104862126195802</v>
       </c>
       <c r="E5" t="n">
-        <v>10.30160588505072</v>
+        <v>1.674010956320741</v>
       </c>
       <c r="F5" t="n">
-        <v>14.88017231015632</v>
+        <v>2.418028000400402</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.55275368011015</v>
+        <v>5.4523224730179</v>
       </c>
       <c r="D6" t="n">
-        <v>29.97548572200965</v>
+        <v>4.871016429826568</v>
       </c>
       <c r="E6" t="n">
-        <v>10.30160588505072</v>
+        <v>1.674010956320741</v>
       </c>
       <c r="F6" t="n">
-        <v>14.88017231015632</v>
+        <v>2.418028000400402</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.95484471892532</v>
+        <v>6.330162266825365</v>
       </c>
       <c r="D7" t="n">
-        <v>14.28891476429733</v>
+        <v>2.321948649198316</v>
       </c>
       <c r="E7" t="n">
-        <v>10.30160588505072</v>
+        <v>1.674010956320741</v>
       </c>
       <c r="F7" t="n">
-        <v>14.88017231015632</v>
+        <v>2.418028000400402</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.96362116591148</v>
+        <v>9.094088439460615</v>
       </c>
       <c r="D8" t="n">
-        <v>23.53136492905883</v>
+        <v>3.82384680097206</v>
       </c>
       <c r="E8" t="n">
-        <v>10.30160588505072</v>
+        <v>1.674010956320741</v>
       </c>
       <c r="F8" t="n">
-        <v>14.88017231015632</v>
+        <v>2.418028000400402</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.34096365093492</v>
+        <v>6.880406593276924</v>
       </c>
       <c r="D9" t="n">
-        <v>44.1868760020986</v>
+        <v>7.180367350341022</v>
       </c>
       <c r="E9" t="n">
-        <v>10.30160588505072</v>
+        <v>1.674010956320741</v>
       </c>
       <c r="F9" t="n">
-        <v>14.88017231015632</v>
+        <v>2.418028000400402</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
